--- a/7203.T_settings.xlsx
+++ b/7203.T_settings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AverageProfit</t>
+          <t>ProfitPerTrade</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,12 +464,27 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>FinalCapital</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TotalCommission</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AverageHoldDays</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MaxDrawdown</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Eligible</t>
         </is>
       </c>
     </row>
@@ -491,33 +506,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>16.77028517598319</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.795047529330531</v>
+      </c>
+      <c r="I2" t="n">
+        <v>167702.8517598319</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1167702.851759832</v>
+      </c>
+      <c r="K2" t="n">
+        <v>12931.60975526324</v>
+      </c>
+      <c r="L2" t="n">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6.064176218356765</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -525,46 +541,47 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>15.14872090991582</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.164102987130831</v>
+      </c>
+      <c r="I3" t="n">
+        <v>151487.2090991582</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1151487.209099158</v>
+      </c>
+      <c r="K3" t="n">
+        <v>14677.37948446385</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.064176218356765</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -572,46 +589,47 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>14.44106811836089</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.406844686393482</v>
+      </c>
+      <c r="I4" t="n">
+        <v>144410.6811836089</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1144410.681183609</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12736.08454355252</v>
+      </c>
+      <c r="L4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7.93791423950023</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -623,42 +641,43 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>14.44106811836089</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.406844686393482</v>
+      </c>
+      <c r="I5" t="n">
+        <v>144410.6811836089</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1144410.681183609</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12736.08454355252</v>
+      </c>
+      <c r="L5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7.93791423950023</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +685,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -679,33 +698,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>11.07093561908256</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.581562231297508</v>
+      </c>
+      <c r="I6" t="n">
+        <v>110709.3561908256</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1110709.356190826</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14272.39918324683</v>
+      </c>
+      <c r="L6" t="n">
+        <v>19.42857142857143</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7.937914239500234</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -722,37 +742,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>11.07093561908256</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.581562231297508</v>
+      </c>
+      <c r="I7" t="n">
+        <v>110709.3561908256</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1110709.356190826</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14272.39918324683</v>
+      </c>
+      <c r="L7" t="n">
+        <v>19.42857142857143</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7.937914239500234</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -760,46 +781,47 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>7.618208882632689</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.523641776526538</v>
+      </c>
+      <c r="I8" t="n">
+        <v>76182.08882632689</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1076182.088826327</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10487.66666444878</v>
+      </c>
+      <c r="L8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5.961855656765596</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -811,42 +833,43 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>7.615326386825484</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4759578991765928</v>
+      </c>
+      <c r="I9" t="n">
+        <v>76153.26386825484</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1076153.263868255</v>
+      </c>
+      <c r="K9" t="n">
+        <v>33713.72045235256</v>
+      </c>
+      <c r="L9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10.82160729199613</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -858,42 +881,43 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>5.52160121313422</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3681067475422813</v>
+      </c>
+      <c r="I10" t="n">
+        <v>55216.0121313422</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1055216.012131342</v>
+      </c>
+      <c r="K10" t="n">
+        <v>31955.51188671577</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>13.15279585864588</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -901,46 +925,47 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5.471550669041624</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.094310133808325</v>
+      </c>
+      <c r="I11" t="n">
+        <v>54715.50669041625</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1054715.506690416</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10340.89095096874</v>
+      </c>
+      <c r="L11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7.837632600474268</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -952,7 +977,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -961,33 +986,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>5.471550669041624</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.094310133808325</v>
+      </c>
+      <c r="I12" t="n">
+        <v>54715.50669041625</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1054715.506690416</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10340.89095096874</v>
+      </c>
+      <c r="L12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7.837632600474268</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -995,46 +1021,47 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0.8824257994665299</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.1260608284952185</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-8824.257994665299</v>
+      </c>
+      <c r="J13" t="n">
+        <v>991175.7420053347</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13493.63007826907</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13.28571428571429</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7.922782197978255</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1042,11 +1069,11 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1055,33 +1082,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-2.271484779041144</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.1419677986900715</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-22714.84779041144</v>
+      </c>
+      <c r="J14" t="n">
+        <v>977285.1522095886</v>
+      </c>
+      <c r="K14" t="n">
+        <v>33371.89873903714</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13.125</v>
+      </c>
+      <c r="M14" t="n">
+        <v>14.62960257955553</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1093,42 +1121,43 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-2.327499504000903</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.1551666336000602</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-23274.99504000903</v>
+      </c>
+      <c r="J15" t="n">
+        <v>976725.004959991</v>
+      </c>
+      <c r="K15" t="n">
+        <v>31485.31099349508</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>15.5307566482056</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1136,46 +1165,47 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-2.859522026749444</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.408503146678492</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-28595.22026749444</v>
+      </c>
+      <c r="J16" t="n">
+        <v>971404.7797325056</v>
+      </c>
+      <c r="K16" t="n">
+        <v>13358.44800431762</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15.71428571428571</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9.759444580037483</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1187,42 +1217,43 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-2.859522026749444</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.408503146678492</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-28595.22026749444</v>
+      </c>
+      <c r="J17" t="n">
+        <v>971404.7797325056</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13358.44800431762</v>
+      </c>
+      <c r="L17" t="n">
+        <v>15.71428571428571</v>
+      </c>
+      <c r="M17" t="n">
+        <v>9.759444580037483</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1234,42 +1265,43 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-4.120675871304225</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.3433896559420187</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-41206.75871304225</v>
+      </c>
+      <c r="J18" t="n">
+        <v>958793.2412869578</v>
+      </c>
+      <c r="K18" t="n">
+        <v>25167.87443172803</v>
+      </c>
+      <c r="L18" t="n">
+        <v>13.83333333333333</v>
+      </c>
+      <c r="M18" t="n">
+        <v>15.97492167906698</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1277,46 +1309,47 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-4.172660670750926</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2781773780500617</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-41726.60670750926</v>
+      </c>
+      <c r="J19" t="n">
+        <v>958273.3932924907</v>
+      </c>
+      <c r="K19" t="n">
+        <v>31624.31111800826</v>
+      </c>
+      <c r="L19" t="n">
+        <v>12</v>
+      </c>
+      <c r="M19" t="n">
+        <v>17.80340075423179</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1324,46 +1357,47 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-4.630863458794239</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.3859052882328532</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-46308.63458794239</v>
+      </c>
+      <c r="J20" t="n">
+        <v>953691.3654120576</v>
+      </c>
+      <c r="K20" t="n">
+        <v>21925.71272416022</v>
+      </c>
+      <c r="L20" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="M20" t="n">
+        <v>18.43760107754678</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1371,11 +1405,11 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1384,33 +1418,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-6.533191771752516</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5444326476460429</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-65331.91771752515</v>
+      </c>
+      <c r="J21" t="n">
+        <v>934668.0822824748</v>
+      </c>
+      <c r="K21" t="n">
+        <v>21694.20697828883</v>
+      </c>
+      <c r="L21" t="n">
+        <v>15.16666666666667</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20.06452637403348</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1418,46 +1453,47 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-7.868820561351988</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.4371566978528882</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-78688.20561351988</v>
+      </c>
+      <c r="J22" t="n">
+        <v>921311.7943864801</v>
+      </c>
+      <c r="K22" t="n">
+        <v>36347.29556210059</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11.27777777777778</v>
+      </c>
+      <c r="M22" t="n">
+        <v>16.92010376835565</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1465,11 +1501,11 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1478,33 +1514,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-9.293918951681174</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.7744932459734312</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-92939.18951681175</v>
+      </c>
+      <c r="J23" t="n">
+        <v>907060.8104831883</v>
+      </c>
+      <c r="K23" t="n">
+        <v>21250.57593719147</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>22.42557880390539</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1512,46 +1549,47 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-9.661107866930321</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.5683004627606071</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-96611.07866930321</v>
+      </c>
+      <c r="J24" t="n">
+        <v>903388.9213306968</v>
+      </c>
+      <c r="K24" t="n">
+        <v>34635.62648314516</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10.17647058823529</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20.00874843886924</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1559,11 +1597,11 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1572,33 +1610,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-10.00495499859172</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.9095413635083379</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-100049.5499859172</v>
+      </c>
+      <c r="J25" t="n">
+        <v>899950.4500140828</v>
+      </c>
+      <c r="K25" t="n">
+        <v>21936.36539021781</v>
+      </c>
+      <c r="L25" t="n">
+        <v>12.63636363636364</v>
+      </c>
+      <c r="M25" t="n">
+        <v>17.65319828244019</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1606,46 +1645,47 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-10.67404137676612</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.7624315269118658</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-106740.4137676612</v>
+      </c>
+      <c r="J26" t="n">
+        <v>893259.5862323388</v>
+      </c>
+      <c r="K26" t="n">
+        <v>26942.92668203331</v>
+      </c>
+      <c r="L26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>13.98444297090588</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1653,11 +1693,11 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1666,33 +1706,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-11.47100051713593</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.5462381198636156</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-114710.0051713593</v>
+      </c>
+      <c r="J27" t="n">
+        <v>885289.9948286407</v>
+      </c>
+      <c r="K27" t="n">
+        <v>37881.0417292147</v>
+      </c>
+      <c r="L27" t="n">
+        <v>13.04761904761905</v>
+      </c>
+      <c r="M27" t="n">
+        <v>20.20772959096987</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1700,7 +1741,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1709,37 +1750,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-11.6444004684151</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.7762933645610068</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-116444.004684151</v>
+      </c>
+      <c r="J28" t="n">
+        <v>883555.995315849</v>
+      </c>
+      <c r="K28" t="n">
+        <v>30769.90501306069</v>
+      </c>
+      <c r="L28" t="n">
+        <v>14.46666666666667</v>
+      </c>
+      <c r="M28" t="n">
+        <v>23.58820957355492</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1760,33 +1802,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-12.26495250786851</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.7665595317417822</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-122649.5250786851</v>
+      </c>
+      <c r="J29" t="n">
+        <v>877350.4749213149</v>
+      </c>
+      <c r="K29" t="n">
+        <v>33069.01954821546</v>
+      </c>
+      <c r="L29" t="n">
+        <v>12.3125</v>
+      </c>
+      <c r="M29" t="n">
+        <v>24.12487609654611</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1794,46 +1837,47 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-13.26652718979907</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-1.105543932483256</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-132665.2718979907</v>
+      </c>
+      <c r="J30" t="n">
+        <v>867334.7281020093</v>
+      </c>
+      <c r="K30" t="n">
+        <v>24465.60264045259</v>
+      </c>
+      <c r="L30" t="n">
+        <v>13.41666666666667</v>
+      </c>
+      <c r="M30" t="n">
+        <v>23.99000606072815</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1845,42 +1889,43 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-13.87568647032673</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-1.067360497717441</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-138756.8647032673</v>
+      </c>
+      <c r="J31" t="n">
+        <v>861243.1352967327</v>
+      </c>
+      <c r="K31" t="n">
+        <v>26600.38758813683</v>
+      </c>
+      <c r="L31" t="n">
+        <v>10.84615384615385</v>
+      </c>
+      <c r="M31" t="n">
+        <v>24.52385062754588</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1888,46 +1933,47 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-17.36401302403923</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.8682006512019615</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-173640.1302403923</v>
+      </c>
+      <c r="J32" t="n">
+        <v>826359.8697596077</v>
+      </c>
+      <c r="K32" t="n">
+        <v>34052.72444354442</v>
+      </c>
+      <c r="L32" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="M32" t="n">
+        <v>25.51917386596863</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1935,46 +1981,47 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-18.58967537187393</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-1.689970488352175</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-185896.7537187393</v>
+      </c>
+      <c r="J33" t="n">
+        <v>814103.2462812607</v>
+      </c>
+      <c r="K33" t="n">
+        <v>21277.18050472202</v>
+      </c>
+      <c r="L33" t="n">
+        <v>12.18181818181818</v>
+      </c>
+      <c r="M33" t="n">
+        <v>25.50834482265586</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1982,46 +2029,47 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-19.10266465265142</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.955133232632571</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-191026.6465265142</v>
+      </c>
+      <c r="J34" t="n">
+        <v>808973.3534734858</v>
+      </c>
+      <c r="K34" t="n">
+        <v>33963.29855041418</v>
+      </c>
+      <c r="L34" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="M34" t="n">
+        <v>25.51917386596863</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2042,33 +2090,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-19.1614501473211</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-1.596787512276758</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-191614.501473211</v>
+      </c>
+      <c r="J35" t="n">
+        <v>808385.498526789</v>
+      </c>
+      <c r="K35" t="n">
+        <v>23283.53293806276</v>
+      </c>
+      <c r="L35" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>26.03152722742175</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2076,46 +2125,47 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-19.19477245068922</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-1.37105517504923</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-191947.7245068923</v>
+      </c>
+      <c r="J36" t="n">
+        <v>808052.2754931077</v>
+      </c>
+      <c r="K36" t="n">
+        <v>26288.655268047</v>
+      </c>
+      <c r="L36" t="n">
+        <v>13.14285714285714</v>
+      </c>
+      <c r="M36" t="n">
+        <v>22.18939750948471</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2123,46 +2173,47 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-19.40722451031982</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1.492863423870756</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-194072.2451031982</v>
+      </c>
+      <c r="J37" t="n">
+        <v>805927.7548968018</v>
+      </c>
+      <c r="K37" t="n">
+        <v>24182.89920876926</v>
+      </c>
+      <c r="L37" t="n">
+        <v>12.76923076923077</v>
+      </c>
+      <c r="M37" t="n">
+        <v>22.39397613962494</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2170,46 +2221,47 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-19.60415330707284</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.9335311098606115</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-196041.5330707284</v>
+      </c>
+      <c r="J38" t="n">
+        <v>803958.4669292716</v>
+      </c>
+      <c r="K38" t="n">
+        <v>37632.9117401577</v>
+      </c>
+      <c r="L38" t="n">
+        <v>12.76190476190476</v>
+      </c>
+      <c r="M38" t="n">
+        <v>19.60415330707284</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2221,42 +2273,43 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-19.76229560734325</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-1.317486373822883</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-197622.9560734325</v>
+      </c>
+      <c r="J39" t="n">
+        <v>802377.0439265675</v>
+      </c>
+      <c r="K39" t="n">
+        <v>28351.85527146977</v>
+      </c>
+      <c r="L39" t="n">
+        <v>10.93333333333333</v>
+      </c>
+      <c r="M39" t="n">
+        <v>22.73588837506169</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2264,46 +2317,47 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>30.43478260869566</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-24.20877201458175</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-1.052555304981815</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-242087.7201458175</v>
+      </c>
+      <c r="J40" t="n">
+        <v>757912.2798541825</v>
+      </c>
+      <c r="K40" t="n">
+        <v>40094.83346511199</v>
+      </c>
+      <c r="L40" t="n">
+        <v>11.34782608695652</v>
+      </c>
+      <c r="M40" t="n">
+        <v>24.20877201458175</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2320,37 +2374,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-24.95577518049307</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1.247788759024654</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-249557.7518049307</v>
+      </c>
+      <c r="J41" t="n">
+        <v>750442.2481950693</v>
+      </c>
+      <c r="K41" t="n">
+        <v>33822.10372131885</v>
+      </c>
+      <c r="L41" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="M41" t="n">
+        <v>24.95577518049307</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2362,7 +2417,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2371,33 +2426,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-26.53484652910703</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-1.326742326455352</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-265348.4652910703</v>
+      </c>
+      <c r="J42" t="n">
+        <v>734651.5347089297</v>
+      </c>
+      <c r="K42" t="n">
+        <v>33740.71008773306</v>
+      </c>
+      <c r="L42" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="M42" t="n">
+        <v>26.53484652910703</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2409,42 +2465,43 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-27.09505267546814</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-2.084234821189857</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-270950.5267546814</v>
+      </c>
+      <c r="J43" t="n">
+        <v>729049.4732453186</v>
+      </c>
+      <c r="K43" t="n">
+        <v>23592.58293655535</v>
+      </c>
+      <c r="L43" t="n">
+        <v>12.38461538461539</v>
+      </c>
+      <c r="M43" t="n">
+        <v>29.79689497935841</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2452,11 +2509,11 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2465,33 +2522,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-27.60709104499789</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-1.971935074642706</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-276070.9104499789</v>
+      </c>
+      <c r="J44" t="n">
+        <v>723929.0895500211</v>
+      </c>
+      <c r="K44" t="n">
+        <v>25430.486644587</v>
+      </c>
+      <c r="L44" t="n">
+        <v>10.07142857142857</v>
+      </c>
+      <c r="M44" t="n">
+        <v>30.28995731257266</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2499,11 +2557,11 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2512,33 +2570,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-29.25388330060826</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-1.329721968209466</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-292538.8330060826</v>
+      </c>
+      <c r="J45" t="n">
+        <v>707461.1669939174</v>
+      </c>
+      <c r="K45" t="n">
+        <v>36129.15223953185</v>
+      </c>
+      <c r="L45" t="n">
+        <v>10.45454545454546</v>
+      </c>
+      <c r="M45" t="n">
+        <v>29.25388330060826</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2546,11 +2605,11 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2559,33 +2618,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>-30.74251438680306</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0円</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>0日</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-1.397387017581957</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-307425.1438680306</v>
+      </c>
+      <c r="J46" t="n">
+        <v>692574.8561319694</v>
+      </c>
+      <c r="K46" t="n">
+        <v>36020.00458555536</v>
+      </c>
+      <c r="L46" t="n">
+        <v>10.27272727272727</v>
+      </c>
+      <c r="M46" t="n">
+        <v>30.74251438680306</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/7203.T_settings.xlsx
+++ b/7203.T_settings.xlsx
@@ -509,28 +509,28 @@
         <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>16.77028517598319</v>
+        <v>16.77029066978923</v>
       </c>
       <c r="G2" t="n">
         <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.795047529330531</v>
+        <v>2.795048444964872</v>
       </c>
       <c r="I2" t="n">
-        <v>167702.8517598319</v>
+        <v>167702.9066978924</v>
       </c>
       <c r="J2" t="n">
-        <v>1167702.851759832</v>
+        <v>1167702.906697892</v>
       </c>
       <c r="K2" t="n">
-        <v>12931.60975526324</v>
+        <v>12931.61056433475</v>
       </c>
       <c r="L2" t="n">
         <v>16.66666666666667</v>
       </c>
       <c r="M2" t="n">
-        <v>6.064176218356765</v>
+        <v>6.064169717776719</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -557,28 +557,28 @@
         <v>42.85714285714285</v>
       </c>
       <c r="F3" t="n">
-        <v>15.14872090991582</v>
+        <v>15.14871875077619</v>
       </c>
       <c r="G3" t="n">
         <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>2.164102987130831</v>
+        <v>2.164102678682313</v>
       </c>
       <c r="I3" t="n">
-        <v>151487.2090991582</v>
+        <v>151487.1875077619</v>
       </c>
       <c r="J3" t="n">
-        <v>1151487.209099158</v>
+        <v>1151487.187507762</v>
       </c>
       <c r="K3" t="n">
-        <v>14677.37948446385</v>
+        <v>14677.37937828159</v>
       </c>
       <c r="L3" t="n">
         <v>16</v>
       </c>
       <c r="M3" t="n">
-        <v>6.064176218356765</v>
+        <v>6.064169717776716</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -605,28 +605,28 @@
         <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>14.44106811836089</v>
+        <v>14.4410624864175</v>
       </c>
       <c r="G4" t="n">
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.406844686393482</v>
+        <v>2.40684374773625</v>
       </c>
       <c r="I4" t="n">
-        <v>144410.6811836089</v>
+        <v>144410.624864175</v>
       </c>
       <c r="J4" t="n">
-        <v>1144410.681183609</v>
+        <v>1144410.624864175</v>
       </c>
       <c r="K4" t="n">
-        <v>12736.08454355252</v>
+        <v>12736.08441446852</v>
       </c>
       <c r="L4" t="n">
         <v>19.5</v>
       </c>
       <c r="M4" t="n">
-        <v>7.93791423950023</v>
+        <v>7.937916730537917</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -653,28 +653,28 @@
         <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>14.44106811836089</v>
+        <v>14.4410624864175</v>
       </c>
       <c r="G5" t="n">
         <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.406844686393482</v>
+        <v>2.40684374773625</v>
       </c>
       <c r="I5" t="n">
-        <v>144410.6811836089</v>
+        <v>144410.624864175</v>
       </c>
       <c r="J5" t="n">
-        <v>1144410.681183609</v>
+        <v>1144410.624864175</v>
       </c>
       <c r="K5" t="n">
-        <v>12736.08454355252</v>
+        <v>12736.08441446852</v>
       </c>
       <c r="L5" t="n">
         <v>19.5</v>
       </c>
       <c r="M5" t="n">
-        <v>7.93791423950023</v>
+        <v>7.937916730537917</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -701,28 +701,28 @@
         <v>42.85714285714285</v>
       </c>
       <c r="F6" t="n">
-        <v>11.07093561908256</v>
+        <v>11.07093720922896</v>
       </c>
       <c r="G6" t="n">
         <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.581562231297508</v>
+        <v>1.58156245846128</v>
       </c>
       <c r="I6" t="n">
-        <v>110709.3561908256</v>
+        <v>110709.3720922896</v>
       </c>
       <c r="J6" t="n">
-        <v>1110709.356190826</v>
+        <v>1110709.37209229</v>
       </c>
       <c r="K6" t="n">
-        <v>14272.39918324683</v>
+        <v>14272.39989998419</v>
       </c>
       <c r="L6" t="n">
         <v>19.42857142857143</v>
       </c>
       <c r="M6" t="n">
-        <v>7.937914239500234</v>
+        <v>7.937916730537921</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -749,28 +749,28 @@
         <v>42.85714285714285</v>
       </c>
       <c r="F7" t="n">
-        <v>11.07093561908256</v>
+        <v>11.07093720922896</v>
       </c>
       <c r="G7" t="n">
         <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>1.581562231297508</v>
+        <v>1.58156245846128</v>
       </c>
       <c r="I7" t="n">
-        <v>110709.3561908256</v>
+        <v>110709.3720922896</v>
       </c>
       <c r="J7" t="n">
-        <v>1110709.356190826</v>
+        <v>1110709.37209229</v>
       </c>
       <c r="K7" t="n">
-        <v>14272.39918324683</v>
+        <v>14272.39989998419</v>
       </c>
       <c r="L7" t="n">
         <v>19.42857142857143</v>
       </c>
       <c r="M7" t="n">
-        <v>7.937914239500234</v>
+        <v>7.937916730537921</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -797,28 +797,28 @@
         <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>7.618208882632689</v>
+        <v>7.618233517347556</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.523641776526538</v>
+        <v>1.523646703469511</v>
       </c>
       <c r="I8" t="n">
-        <v>76182.08882632689</v>
+        <v>76182.33517347556</v>
       </c>
       <c r="J8" t="n">
-        <v>1076182.088826327</v>
+        <v>1076182.335173476</v>
       </c>
       <c r="K8" t="n">
-        <v>10487.66666444878</v>
+        <v>10487.66834202523</v>
       </c>
       <c r="L8" t="n">
         <v>16.2</v>
       </c>
       <c r="M8" t="n">
-        <v>5.961855656765596</v>
+        <v>5.961840179124227</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -845,28 +845,28 @@
         <v>37.5</v>
       </c>
       <c r="F9" t="n">
-        <v>7.615326386825484</v>
+        <v>7.615335771957087</v>
       </c>
       <c r="G9" t="n">
         <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4759578991765928</v>
+        <v>0.4759584857473179</v>
       </c>
       <c r="I9" t="n">
-        <v>76153.26386825484</v>
+        <v>76153.35771957086</v>
       </c>
       <c r="J9" t="n">
-        <v>1076153.263868255</v>
+        <v>1076153.357719571</v>
       </c>
       <c r="K9" t="n">
-        <v>33713.72045235256</v>
+        <v>33713.72374587307</v>
       </c>
       <c r="L9" t="n">
         <v>13.5</v>
       </c>
       <c r="M9" t="n">
-        <v>10.82160729199613</v>
+        <v>10.82159003812014</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -893,28 +893,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>5.52160121313422</v>
+        <v>5.521616220915225</v>
       </c>
       <c r="G10" t="n">
         <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3681067475422813</v>
+        <v>0.368107748061015</v>
       </c>
       <c r="I10" t="n">
-        <v>55216.0121313422</v>
+        <v>55216.16220915224</v>
       </c>
       <c r="J10" t="n">
-        <v>1055216.012131342</v>
+        <v>1055216.162209152</v>
       </c>
       <c r="K10" t="n">
-        <v>31955.51188671577</v>
+        <v>31955.51577841409</v>
       </c>
       <c r="L10" t="n">
         <v>12.4</v>
       </c>
       <c r="M10" t="n">
-        <v>13.15279585864588</v>
+        <v>13.15278701386504</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -941,28 +941,28 @@
         <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>5.471550669041624</v>
+        <v>5.47156465983151</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.094310133808325</v>
+        <v>1.094312931966302</v>
       </c>
       <c r="I11" t="n">
-        <v>54715.50669041625</v>
+        <v>54715.6465983151</v>
       </c>
       <c r="J11" t="n">
-        <v>1054715.506690416</v>
+        <v>1054715.646598315</v>
       </c>
       <c r="K11" t="n">
-        <v>10340.89095096874</v>
+        <v>10340.89190364323</v>
       </c>
       <c r="L11" t="n">
         <v>19.6</v>
       </c>
       <c r="M11" t="n">
-        <v>7.837632600474268</v>
+        <v>7.837626302978904</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -989,28 +989,28 @@
         <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>5.471550669041624</v>
+        <v>5.47156465983151</v>
       </c>
       <c r="G12" t="n">
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.094310133808325</v>
+        <v>1.094312931966302</v>
       </c>
       <c r="I12" t="n">
-        <v>54715.50669041625</v>
+        <v>54715.6465983151</v>
       </c>
       <c r="J12" t="n">
-        <v>1054715.506690416</v>
+        <v>1054715.646598315</v>
       </c>
       <c r="K12" t="n">
-        <v>10340.89095096874</v>
+        <v>10340.89190364323</v>
       </c>
       <c r="L12" t="n">
         <v>19.6</v>
       </c>
       <c r="M12" t="n">
-        <v>7.837632600474268</v>
+        <v>7.837626302978904</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1037,28 +1037,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8824257994665299</v>
+        <v>-0.8824094835443306</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1260608284952185</v>
+        <v>-0.1260584976491901</v>
       </c>
       <c r="I13" t="n">
-        <v>-8824.257994665299</v>
+        <v>-8824.094835443306</v>
       </c>
       <c r="J13" t="n">
-        <v>991175.7420053347</v>
+        <v>991175.9051645567</v>
       </c>
       <c r="K13" t="n">
-        <v>13493.63007826907</v>
+        <v>13493.63106730588</v>
       </c>
       <c r="L13" t="n">
         <v>13.28571428571429</v>
       </c>
       <c r="M13" t="n">
-        <v>7.922782197978255</v>
+        <v>7.922767040981784</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1085,28 +1085,28 @@
         <v>31.25</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.271484779041144</v>
+        <v>-2.271454208529101</v>
       </c>
       <c r="G14" t="n">
         <v>16</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1419677986900715</v>
+        <v>-0.1419658880330688</v>
       </c>
       <c r="I14" t="n">
-        <v>-22714.84779041144</v>
+        <v>-22714.542085291</v>
       </c>
       <c r="J14" t="n">
-        <v>977285.1522095886</v>
+        <v>977285.457914709</v>
       </c>
       <c r="K14" t="n">
-        <v>33371.89873903714</v>
+        <v>33371.90700683621</v>
       </c>
       <c r="L14" t="n">
         <v>13.125</v>
       </c>
       <c r="M14" t="n">
-        <v>14.62960257955553</v>
+        <v>14.62960257955552</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1133,28 +1133,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.327499504000903</v>
+        <v>-2.327500808117015</v>
       </c>
       <c r="G15" t="n">
         <v>15</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1551666336000602</v>
+        <v>-0.1551667205411343</v>
       </c>
       <c r="I15" t="n">
-        <v>-23274.99504000903</v>
+        <v>-23275.00808117015</v>
       </c>
       <c r="J15" t="n">
-        <v>976725.004959991</v>
+        <v>976724.9919188299</v>
       </c>
       <c r="K15" t="n">
-        <v>31485.31099349508</v>
+        <v>31485.31365315145</v>
       </c>
       <c r="L15" t="n">
         <v>14.8</v>
       </c>
       <c r="M15" t="n">
-        <v>15.5307566482056</v>
+        <v>15.5307802900091</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1181,28 +1181,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.859522026749444</v>
+        <v>-2.859515386880014</v>
       </c>
       <c r="G16" t="n">
         <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.408503146678492</v>
+        <v>-0.4085021981257163</v>
       </c>
       <c r="I16" t="n">
-        <v>-28595.22026749444</v>
+        <v>-28595.15386880015</v>
       </c>
       <c r="J16" t="n">
-        <v>971404.7797325056</v>
+        <v>971404.8461311999</v>
       </c>
       <c r="K16" t="n">
-        <v>13358.44800431762</v>
+        <v>13358.44833440341</v>
       </c>
       <c r="L16" t="n">
         <v>15.71428571428571</v>
       </c>
       <c r="M16" t="n">
-        <v>9.759444580037483</v>
+        <v>9.75943841180033</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1229,28 +1229,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.859522026749444</v>
+        <v>-2.859515386880014</v>
       </c>
       <c r="G17" t="n">
         <v>7</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.408503146678492</v>
+        <v>-0.4085021981257163</v>
       </c>
       <c r="I17" t="n">
-        <v>-28595.22026749444</v>
+        <v>-28595.15386880015</v>
       </c>
       <c r="J17" t="n">
-        <v>971404.7797325056</v>
+        <v>971404.8461311999</v>
       </c>
       <c r="K17" t="n">
-        <v>13358.44800431762</v>
+        <v>13358.44833440341</v>
       </c>
       <c r="L17" t="n">
         <v>15.71428571428571</v>
       </c>
       <c r="M17" t="n">
-        <v>9.759444580037483</v>
+        <v>9.75943841180033</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1277,28 +1277,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.120675871304225</v>
+        <v>-4.120671984805655</v>
       </c>
       <c r="G18" t="n">
         <v>12</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3433896559420187</v>
+        <v>-0.343389332067138</v>
       </c>
       <c r="I18" t="n">
-        <v>-41206.75871304225</v>
+        <v>-41206.71984805656</v>
       </c>
       <c r="J18" t="n">
-        <v>958793.2412869578</v>
+        <v>958793.2801519434</v>
       </c>
       <c r="K18" t="n">
-        <v>25167.87443172803</v>
+        <v>25167.87592159252</v>
       </c>
       <c r="L18" t="n">
         <v>13.83333333333333</v>
       </c>
       <c r="M18" t="n">
-        <v>15.97492167906698</v>
+        <v>15.97492969410767</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1325,28 +1325,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.172660670750926</v>
+        <v>-4.172625423029764</v>
       </c>
       <c r="G19" t="n">
         <v>15</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2781773780500617</v>
+        <v>-0.2781750282019843</v>
       </c>
       <c r="I19" t="n">
-        <v>-41726.60670750926</v>
+        <v>-41726.25423029764</v>
       </c>
       <c r="J19" t="n">
-        <v>958273.3932924907</v>
+        <v>958273.7457697024</v>
       </c>
       <c r="K19" t="n">
-        <v>31624.31111800826</v>
+        <v>31624.31996522365</v>
       </c>
       <c r="L19" t="n">
         <v>12</v>
       </c>
       <c r="M19" t="n">
-        <v>17.80340075423179</v>
+        <v>17.80339238308257</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1373,28 +1373,28 @@
         <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.630863458794239</v>
+        <v>-4.630873785117188</v>
       </c>
       <c r="G20" t="n">
         <v>12</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3859052882328532</v>
+        <v>-0.3859061487597656</v>
       </c>
       <c r="I20" t="n">
-        <v>-46308.63458794239</v>
+        <v>-46308.73785117187</v>
       </c>
       <c r="J20" t="n">
-        <v>953691.3654120576</v>
+        <v>953691.2621488281</v>
       </c>
       <c r="K20" t="n">
-        <v>21925.71272416022</v>
+        <v>21925.71198614893</v>
       </c>
       <c r="L20" t="n">
         <v>13.75</v>
       </c>
       <c r="M20" t="n">
-        <v>18.43760107754678</v>
+        <v>18.43760285590059</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1421,28 +1421,28 @@
         <v>25</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.533191771752516</v>
+        <v>-6.533210889264766</v>
       </c>
       <c r="G21" t="n">
         <v>12</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5444326476460429</v>
+        <v>-0.5444342407720638</v>
       </c>
       <c r="I21" t="n">
-        <v>-65331.91771752515</v>
+        <v>-65332.10889264767</v>
       </c>
       <c r="J21" t="n">
-        <v>934668.0822824748</v>
+        <v>934667.8911073523</v>
       </c>
       <c r="K21" t="n">
-        <v>21694.20697828883</v>
+        <v>21694.20515389108</v>
       </c>
       <c r="L21" t="n">
         <v>15.16666666666667</v>
       </c>
       <c r="M21" t="n">
-        <v>20.06452637403348</v>
+        <v>20.06453581154959</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1469,28 +1469,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.868820561351988</v>
+        <v>-7.868763674368127</v>
       </c>
       <c r="G22" t="n">
         <v>18</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4371566978528882</v>
+        <v>-0.4371535374648959</v>
       </c>
       <c r="I22" t="n">
-        <v>-78688.20561351988</v>
+        <v>-78687.63674368127</v>
       </c>
       <c r="J22" t="n">
-        <v>921311.7943864801</v>
+        <v>921312.3632563187</v>
       </c>
       <c r="K22" t="n">
-        <v>36347.29556210059</v>
+        <v>36347.31443421676</v>
       </c>
       <c r="L22" t="n">
         <v>11.27777777777778</v>
       </c>
       <c r="M22" t="n">
-        <v>16.92010376835565</v>
+        <v>16.92010376835566</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -1517,28 +1517,28 @@
         <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.293918951681174</v>
+        <v>-9.293937303808937</v>
       </c>
       <c r="G23" t="n">
         <v>12</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7744932459734312</v>
+        <v>-0.7744947753174114</v>
       </c>
       <c r="I23" t="n">
-        <v>-92939.18951681175</v>
+        <v>-92939.37303808937</v>
       </c>
       <c r="J23" t="n">
-        <v>907060.8104831883</v>
+        <v>907060.6269619106</v>
       </c>
       <c r="K23" t="n">
-        <v>21250.57593719147</v>
+        <v>21250.57419237157</v>
       </c>
       <c r="L23" t="n">
         <v>15.25</v>
       </c>
       <c r="M23" t="n">
-        <v>22.42557880390539</v>
+        <v>22.42558779101207</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -1565,28 +1565,28 @@
         <v>35.29411764705883</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.661107866930321</v>
+        <v>-9.661047116632689</v>
       </c>
       <c r="G24" t="n">
         <v>17</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5683004627606071</v>
+        <v>-0.5682968892136876</v>
       </c>
       <c r="I24" t="n">
-        <v>-96611.07866930321</v>
+        <v>-96610.4711663269</v>
       </c>
       <c r="J24" t="n">
-        <v>903388.9213306968</v>
+        <v>903389.5288336731</v>
       </c>
       <c r="K24" t="n">
-        <v>34635.62648314516</v>
+        <v>34635.64548667576</v>
       </c>
       <c r="L24" t="n">
         <v>10.17647058823529</v>
       </c>
       <c r="M24" t="n">
-        <v>20.00874843886924</v>
+        <v>20.00874029231931</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -1613,22 +1613,22 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.00495499859172</v>
+        <v>-10.00497118637548</v>
       </c>
       <c r="G25" t="n">
         <v>11</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9095413635083379</v>
+        <v>-0.9095428351250436</v>
       </c>
       <c r="I25" t="n">
-        <v>-100049.5499859172</v>
+        <v>-100049.7118637548</v>
       </c>
       <c r="J25" t="n">
-        <v>899950.4500140828</v>
+        <v>899950.2881362452</v>
       </c>
       <c r="K25" t="n">
-        <v>21936.36539021781</v>
+        <v>21936.36188921935</v>
       </c>
       <c r="L25" t="n">
         <v>12.63636363636364</v>
@@ -1661,28 +1661,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.67404137676612</v>
+        <v>-10.6740397633052</v>
       </c>
       <c r="G26" t="n">
         <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7624315269118658</v>
+        <v>-0.7624314116646568</v>
       </c>
       <c r="I26" t="n">
-        <v>-106740.4137676612</v>
+        <v>-106740.397633052</v>
       </c>
       <c r="J26" t="n">
-        <v>893259.5862323388</v>
+        <v>893259.602366948</v>
       </c>
       <c r="K26" t="n">
-        <v>26942.92668203331</v>
+        <v>26942.92869019421</v>
       </c>
       <c r="L26" t="n">
         <v>13.5</v>
       </c>
       <c r="M26" t="n">
-        <v>13.98444297090588</v>
+        <v>13.98445861390809</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -1709,28 +1709,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.47100051713593</v>
+        <v>-11.47094635683228</v>
       </c>
       <c r="G27" t="n">
         <v>21</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5462381198636156</v>
+        <v>-0.5462355408015372</v>
       </c>
       <c r="I27" t="n">
-        <v>-114710.0051713593</v>
+        <v>-114709.4635683228</v>
       </c>
       <c r="J27" t="n">
-        <v>885289.9948286407</v>
+        <v>885290.5364316772</v>
       </c>
       <c r="K27" t="n">
-        <v>37881.0417292147</v>
+        <v>37881.06222694137</v>
       </c>
       <c r="L27" t="n">
         <v>13.04761904761905</v>
       </c>
       <c r="M27" t="n">
-        <v>20.20772959096987</v>
+        <v>20.20767387566028</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -1757,28 +1757,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>-11.6444004684151</v>
+        <v>-11.64440164813261</v>
       </c>
       <c r="G28" t="n">
         <v>15</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7762933645610068</v>
+        <v>-0.7762934432088405</v>
       </c>
       <c r="I28" t="n">
-        <v>-116444.004684151</v>
+        <v>-116444.0164813261</v>
       </c>
       <c r="J28" t="n">
-        <v>883555.995315849</v>
+        <v>883555.9835186739</v>
       </c>
       <c r="K28" t="n">
-        <v>30769.90501306069</v>
+        <v>30769.90768226911</v>
       </c>
       <c r="L28" t="n">
         <v>14.46666666666667</v>
       </c>
       <c r="M28" t="n">
-        <v>23.58820957355492</v>
+        <v>23.58823096018585</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -1805,28 +1805,28 @@
         <v>31.25</v>
       </c>
       <c r="F29" t="n">
-        <v>-12.26495250786851</v>
+        <v>-12.26494523387292</v>
       </c>
       <c r="G29" t="n">
         <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7665595317417822</v>
+        <v>-0.7665590771170574</v>
       </c>
       <c r="I29" t="n">
-        <v>-122649.5250786851</v>
+        <v>-122649.4523387292</v>
       </c>
       <c r="J29" t="n">
-        <v>877350.4749213149</v>
+        <v>877350.5476612708</v>
       </c>
       <c r="K29" t="n">
-        <v>33069.01954821546</v>
+        <v>33069.02429078849</v>
       </c>
       <c r="L29" t="n">
         <v>12.3125</v>
       </c>
       <c r="M29" t="n">
-        <v>24.12487609654611</v>
+        <v>24.12489002918897</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F30" t="n">
-        <v>-13.26652718979907</v>
+        <v>-13.26652367403049</v>
       </c>
       <c r="G30" t="n">
         <v>12</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.105543932483256</v>
+        <v>-1.10554363950254</v>
       </c>
       <c r="I30" t="n">
-        <v>-132665.2718979907</v>
+        <v>-132665.2367403049</v>
       </c>
       <c r="J30" t="n">
-        <v>867334.7281020093</v>
+        <v>867334.7632596951</v>
       </c>
       <c r="K30" t="n">
-        <v>24465.60264045259</v>
+        <v>24465.60410185028</v>
       </c>
       <c r="L30" t="n">
         <v>13.41666666666667</v>
       </c>
       <c r="M30" t="n">
-        <v>23.99000606072815</v>
+        <v>23.9900133112206</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -1901,28 +1901,28 @@
         <v>30.76923076923077</v>
       </c>
       <c r="F31" t="n">
-        <v>-13.87568647032673</v>
+        <v>-13.87567468887286</v>
       </c>
       <c r="G31" t="n">
         <v>13</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.067360497717441</v>
+        <v>-1.067359591451758</v>
       </c>
       <c r="I31" t="n">
-        <v>-138756.8647032673</v>
+        <v>-138756.7468887286</v>
       </c>
       <c r="J31" t="n">
-        <v>861243.1352967327</v>
+        <v>861243.2531112714</v>
       </c>
       <c r="K31" t="n">
-        <v>26600.38758813683</v>
+        <v>26600.39058918555</v>
       </c>
       <c r="L31" t="n">
         <v>10.84615384615385</v>
       </c>
       <c r="M31" t="n">
-        <v>24.52385062754588</v>
+        <v>24.52385056173746</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -1949,28 +1949,28 @@
         <v>25</v>
       </c>
       <c r="F32" t="n">
-        <v>-17.36401302403923</v>
+        <v>-17.36399068149844</v>
       </c>
       <c r="G32" t="n">
         <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8682006512019615</v>
+        <v>-0.868199534074922</v>
       </c>
       <c r="I32" t="n">
-        <v>-173640.1302403923</v>
+        <v>-173639.9068149844</v>
       </c>
       <c r="J32" t="n">
-        <v>826359.8697596077</v>
+        <v>826360.0931850156</v>
       </c>
       <c r="K32" t="n">
-        <v>34052.72444354442</v>
+        <v>34052.73272033832</v>
       </c>
       <c r="L32" t="n">
         <v>12.15</v>
       </c>
       <c r="M32" t="n">
-        <v>25.51917386596863</v>
+        <v>25.51914728770257</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -1997,28 +1997,28 @@
         <v>18.18181818181818</v>
       </c>
       <c r="F33" t="n">
-        <v>-18.58967537187393</v>
+        <v>-18.58969001548825</v>
       </c>
       <c r="G33" t="n">
         <v>11</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.689970488352175</v>
+        <v>-1.689971819589841</v>
       </c>
       <c r="I33" t="n">
-        <v>-185896.7537187393</v>
+        <v>-185896.9001548825</v>
       </c>
       <c r="J33" t="n">
-        <v>814103.2462812607</v>
+        <v>814103.0998451175</v>
       </c>
       <c r="K33" t="n">
-        <v>21277.18050472202</v>
+        <v>21277.17712229388</v>
       </c>
       <c r="L33" t="n">
         <v>12.18181818181818</v>
       </c>
       <c r="M33" t="n">
-        <v>25.50834482265586</v>
+        <v>25.50834482265585</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2045,28 +2045,28 @@
         <v>25</v>
       </c>
       <c r="F34" t="n">
-        <v>-19.10266465265142</v>
+        <v>-19.10264278019509</v>
       </c>
       <c r="G34" t="n">
         <v>20</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.955133232632571</v>
+        <v>-0.9551321390097547</v>
       </c>
       <c r="I34" t="n">
-        <v>-191026.6465265142</v>
+        <v>-191026.427801951</v>
       </c>
       <c r="J34" t="n">
-        <v>808973.3534734858</v>
+        <v>808973.572198049</v>
       </c>
       <c r="K34" t="n">
-        <v>33963.29855041418</v>
+        <v>33963.30680302973</v>
       </c>
       <c r="L34" t="n">
         <v>11.95</v>
       </c>
       <c r="M34" t="n">
-        <v>25.51917386596863</v>
+        <v>25.51914728770257</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2093,28 +2093,28 @@
         <v>16.66666666666666</v>
       </c>
       <c r="F35" t="n">
-        <v>-19.1614501473211</v>
+        <v>-19.16145690669005</v>
       </c>
       <c r="G35" t="n">
         <v>12</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.596787512276758</v>
+        <v>-1.596788075557504</v>
       </c>
       <c r="I35" t="n">
-        <v>-191614.501473211</v>
+        <v>-191614.5690669005</v>
       </c>
       <c r="J35" t="n">
-        <v>808385.498526789</v>
+        <v>808385.4309330995</v>
       </c>
       <c r="K35" t="n">
-        <v>23283.53293806276</v>
+        <v>23283.53057113339</v>
       </c>
       <c r="L35" t="n">
         <v>9.5</v>
       </c>
       <c r="M35" t="n">
-        <v>26.03152722742175</v>
+        <v>26.03152010732594</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2141,28 +2141,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F36" t="n">
-        <v>-19.19477245068922</v>
+        <v>-19.19477099113503</v>
       </c>
       <c r="G36" t="n">
         <v>14</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.37105517504923</v>
+        <v>-1.371055070795359</v>
       </c>
       <c r="I36" t="n">
-        <v>-191947.7245068923</v>
+        <v>-191947.7099113503</v>
       </c>
       <c r="J36" t="n">
-        <v>808052.2754931077</v>
+        <v>808052.2900886497</v>
       </c>
       <c r="K36" t="n">
-        <v>26288.655268047</v>
+        <v>26288.65726439004</v>
       </c>
       <c r="L36" t="n">
         <v>13.14285714285714</v>
       </c>
       <c r="M36" t="n">
-        <v>22.18939750948471</v>
+        <v>22.18941166031355</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2189,28 +2189,28 @@
         <v>23.07692307692308</v>
       </c>
       <c r="F37" t="n">
-        <v>-19.40722451031982</v>
+        <v>-19.40720839779841</v>
       </c>
       <c r="G37" t="n">
         <v>13</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.492863423870756</v>
+        <v>-1.492862184446032</v>
       </c>
       <c r="I37" t="n">
-        <v>-194072.2451031982</v>
+        <v>-194072.0839779841</v>
       </c>
       <c r="J37" t="n">
-        <v>805927.7548968018</v>
+        <v>805927.9160220159</v>
       </c>
       <c r="K37" t="n">
-        <v>24182.89920876926</v>
+        <v>24182.90315043978</v>
       </c>
       <c r="L37" t="n">
         <v>12.76923076923077</v>
       </c>
       <c r="M37" t="n">
-        <v>22.39397613962494</v>
+        <v>22.39397613962493</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2237,28 +2237,28 @@
         <v>28.57142857142857</v>
       </c>
       <c r="F38" t="n">
-        <v>-19.60415330707284</v>
+        <v>-19.60408598511374</v>
       </c>
       <c r="G38" t="n">
         <v>21</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9335311098606115</v>
+        <v>-0.9335279040530353</v>
       </c>
       <c r="I38" t="n">
-        <v>-196041.5330707284</v>
+        <v>-196040.8598511374</v>
       </c>
       <c r="J38" t="n">
-        <v>803958.4669292716</v>
+        <v>803959.1401488626</v>
       </c>
       <c r="K38" t="n">
-        <v>37632.9117401577</v>
+        <v>37632.93702334637</v>
       </c>
       <c r="L38" t="n">
         <v>12.76190476190476</v>
       </c>
       <c r="M38" t="n">
-        <v>19.60415330707284</v>
+        <v>19.60408598511374</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2285,28 +2285,28 @@
         <v>26.66666666666667</v>
       </c>
       <c r="F39" t="n">
-        <v>-19.76229560734325</v>
+        <v>-19.76228643431091</v>
       </c>
       <c r="G39" t="n">
         <v>15</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.317486373822883</v>
+        <v>-1.317485762287394</v>
       </c>
       <c r="I39" t="n">
-        <v>-197622.9560734325</v>
+        <v>-197622.8643431091</v>
       </c>
       <c r="J39" t="n">
-        <v>802377.0439265675</v>
+        <v>802377.1356568909</v>
       </c>
       <c r="K39" t="n">
-        <v>28351.85527146977</v>
+        <v>28351.8590276194</v>
       </c>
       <c r="L39" t="n">
         <v>10.93333333333333</v>
       </c>
       <c r="M39" t="n">
-        <v>22.73588837506169</v>
+        <v>22.73589498901655</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2333,28 +2333,28 @@
         <v>30.43478260869566</v>
       </c>
       <c r="F40" t="n">
-        <v>-24.20877201458175</v>
+        <v>-24.20868545895119</v>
       </c>
       <c r="G40" t="n">
         <v>23</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.052555304981815</v>
+        <v>-1.05255154169353</v>
       </c>
       <c r="I40" t="n">
-        <v>-242087.7201458175</v>
+        <v>-242086.8545895119</v>
       </c>
       <c r="J40" t="n">
-        <v>757912.2798541825</v>
+        <v>757913.1454104881</v>
       </c>
       <c r="K40" t="n">
-        <v>40094.83346511199</v>
+        <v>40094.87009788378</v>
       </c>
       <c r="L40" t="n">
         <v>11.34782608695652</v>
       </c>
       <c r="M40" t="n">
-        <v>24.20877201458175</v>
+        <v>24.20868545895119</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2381,28 +2381,28 @@
         <v>25</v>
       </c>
       <c r="F41" t="n">
-        <v>-24.95577518049307</v>
+        <v>-24.95573796053659</v>
       </c>
       <c r="G41" t="n">
         <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.247788759024654</v>
+        <v>-1.24778689802683</v>
       </c>
       <c r="I41" t="n">
-        <v>-249557.7518049307</v>
+        <v>-249557.3796053659</v>
       </c>
       <c r="J41" t="n">
-        <v>750442.2481950693</v>
+        <v>750442.6203946341</v>
       </c>
       <c r="K41" t="n">
-        <v>33822.10372131885</v>
+        <v>33822.11656895423</v>
       </c>
       <c r="L41" t="n">
         <v>11.85</v>
       </c>
       <c r="M41" t="n">
-        <v>24.95577518049307</v>
+        <v>24.95573796053659</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>20</v>
       </c>
       <c r="F42" t="n">
-        <v>-26.53484652910703</v>
+        <v>-26.53481009232831</v>
       </c>
       <c r="G42" t="n">
         <v>20</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.326742326455352</v>
+        <v>-1.326740504616416</v>
       </c>
       <c r="I42" t="n">
-        <v>-265348.4652910703</v>
+        <v>-265348.1009232831</v>
       </c>
       <c r="J42" t="n">
-        <v>734651.5347089297</v>
+        <v>734651.8990767169</v>
       </c>
       <c r="K42" t="n">
-        <v>33740.71008773306</v>
+        <v>33740.72289499934</v>
       </c>
       <c r="L42" t="n">
         <v>11.65</v>
       </c>
       <c r="M42" t="n">
-        <v>26.53484652910703</v>
+        <v>26.53481009232831</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2477,22 +2477,22 @@
         <v>15.38461538461539</v>
       </c>
       <c r="F43" t="n">
-        <v>-27.09505267546814</v>
+        <v>-27.0950380999368</v>
       </c>
       <c r="G43" t="n">
         <v>13</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.084234821189857</v>
+        <v>-2.084233699995139</v>
       </c>
       <c r="I43" t="n">
-        <v>-270950.5267546814</v>
+        <v>-270950.380999368</v>
       </c>
       <c r="J43" t="n">
-        <v>729049.4732453186</v>
+        <v>729049.619000632</v>
       </c>
       <c r="K43" t="n">
-        <v>23592.58293655535</v>
+        <v>23592.58676020681</v>
       </c>
       <c r="L43" t="n">
         <v>12.38461538461539</v>
@@ -2525,28 +2525,28 @@
         <v>14.28571428571428</v>
       </c>
       <c r="F44" t="n">
-        <v>-27.60709104499789</v>
+        <v>-27.60706960340014</v>
       </c>
       <c r="G44" t="n">
         <v>14</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.971935074642706</v>
+        <v>-1.97193354310001</v>
       </c>
       <c r="I44" t="n">
-        <v>-276070.9104499789</v>
+        <v>-276070.6960340014</v>
       </c>
       <c r="J44" t="n">
-        <v>723929.0895500211</v>
+        <v>723929.3039659986</v>
       </c>
       <c r="K44" t="n">
-        <v>25430.486644587</v>
+        <v>25430.49226692743</v>
       </c>
       <c r="L44" t="n">
         <v>10.07142857142857</v>
       </c>
       <c r="M44" t="n">
-        <v>30.28995731257266</v>
+        <v>30.28995060238703</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -2573,28 +2573,28 @@
         <v>27.27272727272727</v>
       </c>
       <c r="F45" t="n">
-        <v>-29.25388330060826</v>
+        <v>-29.25382665988825</v>
       </c>
       <c r="G45" t="n">
         <v>22</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.329721968209466</v>
+        <v>-1.329719393631284</v>
       </c>
       <c r="I45" t="n">
-        <v>-292538.8330060826</v>
+        <v>-292538.2665988825</v>
       </c>
       <c r="J45" t="n">
-        <v>707461.1669939174</v>
+        <v>707461.7334011175</v>
       </c>
       <c r="K45" t="n">
-        <v>36129.15223953185</v>
+        <v>36129.17551427903</v>
       </c>
       <c r="L45" t="n">
         <v>10.45454545454546</v>
       </c>
       <c r="M45" t="n">
-        <v>29.25388330060826</v>
+        <v>29.25382665988825</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -2621,28 +2621,28 @@
         <v>22.72727272727273</v>
       </c>
       <c r="F46" t="n">
-        <v>-30.74251438680306</v>
+        <v>-30.74245893791011</v>
       </c>
       <c r="G46" t="n">
         <v>22</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.397387017581957</v>
+        <v>-1.397384497177732</v>
       </c>
       <c r="I46" t="n">
-        <v>-307425.1438680306</v>
+        <v>-307424.5893791012</v>
       </c>
       <c r="J46" t="n">
-        <v>692574.8561319694</v>
+        <v>692575.4106208988</v>
       </c>
       <c r="K46" t="n">
-        <v>36020.00458555536</v>
+        <v>36020.02777291681</v>
       </c>
       <c r="L46" t="n">
         <v>10.27272727272727</v>
       </c>
       <c r="M46" t="n">
-        <v>30.74251438680306</v>
+        <v>30.74245893791011</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
